--- a/data/crawler_log.xlsx
+++ b/data/crawler_log.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
   <si>
     <t>crawlerLogId</t>
   </si>
@@ -87,6 +87,24 @@
   </si>
   <si>
     <t>2026-10-21 09:12:54</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>本次抓到 176 筆、新增 18 筆、略過 0 筆、更新 1 筆、納入審核 1 筆，耗時 36 秒。</t>
+  </si>
+  <si>
+    <t>2026-10-24 23:29:48</t>
+  </si>
+  <si>
+    <t>2026-10-24 23:30:25</t>
   </si>
 </sst>
 </file>
@@ -131,7 +149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -239,6 +257,41 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
